--- a/example_files/bulk_upload_test.xlsx
+++ b/example_files/bulk_upload_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reece\OneDrive\Desktop\reece\MUSHROOM RESEARCH\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5C563B8-06A6-4C1F-942A-AE8DB7F53491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B57D9A7-9089-4744-BCE6-6BC5EFD1A71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="10440" windowWidth="19410" windowHeight="10545" xr2:uid="{B2C4B8A0-44A9-407D-914C-C53E3445315B}"/>
+    <workbookView xWindow="-16365" yWindow="-7380" windowWidth="16530" windowHeight="28410" xr2:uid="{B2C4B8A0-44A9-407D-914C-C53E3445315B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>alternate ID 2</t>
   </si>
   <si>
-    <t>Uehling lab ID Sample ID</t>
-  </si>
-  <si>
     <t>LTS Hempseed</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>Date of sample collection</t>
   </si>
   <si>
-    <t>Assembly Filename</t>
-  </si>
-  <si>
     <t>/nfs4/BPP/Uehling_Lab/data/KTM_assemblies/JKU1_spades.fasta</t>
   </si>
   <si>
@@ -219,6 +213,12 @@
   </si>
   <si>
     <t>UL174</t>
+  </si>
+  <si>
+    <t>Primary Assembly Filename</t>
+  </si>
+  <si>
+    <t>Uehling lab ID</t>
   </si>
 </sst>
 </file>
@@ -778,124 +778,124 @@
         <v>10</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="W1" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="X1" s="16" t="s">
+      <c r="AA1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="Y1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="17" t="s">
+      <c r="AE1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB1" s="17" t="s">
+      <c r="AF1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="AC1" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD1" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="18" t="s">
+      <c r="AH1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AI1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="19" t="s">
+      <c r="AJ1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="19" t="s">
+      <c r="AK1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="20" t="s">
+      <c r="AL1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="20" t="s">
+      <c r="AM1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="19" t="s">
+      <c r="AN1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="19" t="s">
+      <c r="AO1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="20" t="s">
-        <v>40</v>
-      </c>
       <c r="AP1" s="21" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="31.5" thickBot="1">
@@ -967,23 +967,23 @@
       </c>
       <c r="AO2" s="4"/>
       <c r="AP2" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:42" ht="31.5" thickBot="1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -1042,18 +1042,18 @@
     </row>
     <row r="4" spans="1:42" ht="31.5" thickBot="1">
       <c r="A4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -1105,21 +1105,21 @@
       </c>
       <c r="AO4" s="4"/>
       <c r="AP4" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:42" ht="16.5" thickBot="1">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -1154,34 +1154,34 @@
         <v>5</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AJ5" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AK5" s="4"/>
       <c r="AL5" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AM5" s="4"/>
       <c r="AN5" s="4"/>
       <c r="AO5" s="4"/>
       <c r="AP5" s="22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:42" ht="16.5" thickBot="1">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -1223,27 +1223,27 @@
       </c>
       <c r="AK6" s="4"/>
       <c r="AL6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AM6" s="4"/>
       <c r="AN6" s="4"/>
       <c r="AO6" s="4"/>
       <c r="AP6" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:42" ht="16.5" thickBot="1">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1281,13 +1281,13 @@
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4"/>
       <c r="AL7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AM7" s="4"/>
       <c r="AN7" s="4"/>
       <c r="AO7" s="4"/>
       <c r="AP7" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
